--- a/data/nzd0163/nzd0163.xlsx
+++ b/data/nzd0163/nzd0163.xlsx
@@ -16247,7 +16247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B423"/>
+  <dimension ref="A1:B424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20480,6 +20480,16 @@
       </c>
       <c r="B423" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0163/nzd0163.xlsx
+++ b/data/nzd0163/nzd0163.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K405"/>
+  <dimension ref="A1:K406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16231,6 +16231,45 @@
         <v>384.92</v>
       </c>
       <c r="K405" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>360.56</v>
+      </c>
+      <c r="C406" t="n">
+        <v>367.02</v>
+      </c>
+      <c r="D406" t="n">
+        <v>376.65</v>
+      </c>
+      <c r="E406" t="n">
+        <v>370.88</v>
+      </c>
+      <c r="F406" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="G406" t="n">
+        <v>381.1</v>
+      </c>
+      <c r="H406" t="n">
+        <v>382.22</v>
+      </c>
+      <c r="I406" t="n">
+        <v>379.08</v>
+      </c>
+      <c r="J406" t="n">
+        <v>384.25</v>
+      </c>
+      <c r="K406" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -16247,7 +16286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B424"/>
+  <dimension ref="A1:B425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20490,6 +20529,16 @@
       </c>
       <c r="B424" t="n">
         <v>0.9</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>
@@ -20658,28 +20707,28 @@
         <v>0.1573</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04349860832109178</v>
+        <v>-0.04408234725907772</v>
       </c>
       <c r="J2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K2" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007858909215277432</v>
+        <v>0.008111339468876988</v>
       </c>
       <c r="M2" t="n">
-        <v>2.838578148254074</v>
+        <v>2.8341706949959</v>
       </c>
       <c r="N2" t="n">
-        <v>12.55880324716251</v>
+        <v>12.5309158607365</v>
       </c>
       <c r="O2" t="n">
-        <v>3.543840183637308</v>
+        <v>3.539903368841655</v>
       </c>
       <c r="P2" t="n">
-        <v>362.8499546251037</v>
+        <v>362.8560423079612</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -20740,28 +20789,28 @@
         <v>0.1392</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05280245033965716</v>
+        <v>-0.0531789682045142</v>
       </c>
       <c r="J3" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K3" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02443988662761343</v>
+        <v>0.02490787807922323</v>
       </c>
       <c r="M3" t="n">
-        <v>1.936838306983302</v>
+        <v>1.934135717597186</v>
       </c>
       <c r="N3" t="n">
-        <v>5.851259627634854</v>
+        <v>5.838103273297919</v>
       </c>
       <c r="O3" t="n">
-        <v>2.418937706439514</v>
+        <v>2.416216727302813</v>
       </c>
       <c r="P3" t="n">
-        <v>369.1364842701531</v>
+        <v>369.1404108907745</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -20822,28 +20871,28 @@
         <v>0.1896</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04153784594433663</v>
+        <v>-0.04199314393522962</v>
       </c>
       <c r="J4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0206834193003852</v>
+        <v>0.02123369778734552</v>
       </c>
       <c r="M4" t="n">
-        <v>1.541875332257775</v>
+        <v>1.540109968294721</v>
       </c>
       <c r="N4" t="n">
-        <v>4.277260353206165</v>
+        <v>4.268680132187119</v>
       </c>
       <c r="O4" t="n">
-        <v>2.068153851435179</v>
+        <v>2.066078442892989</v>
       </c>
       <c r="P4" t="n">
-        <v>378.6361640518836</v>
+        <v>378.6409178781099</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -20904,28 +20953,28 @@
         <v>0.1049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009022347723105411</v>
+        <v>0.008214857728779508</v>
       </c>
       <c r="J5" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K5" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004370799783638413</v>
+        <v>0.0003641291861912199</v>
       </c>
       <c r="M5" t="n">
-        <v>2.466028151316111</v>
+        <v>2.464285371004699</v>
       </c>
       <c r="N5" t="n">
-        <v>9.746873243974328</v>
+        <v>9.729037762086994</v>
       </c>
       <c r="O5" t="n">
-        <v>3.121998277381704</v>
+        <v>3.119140548626655</v>
       </c>
       <c r="P5" t="n">
-        <v>372.241523814693</v>
+        <v>372.249954923965</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -20986,28 +21035,28 @@
         <v>0.104</v>
       </c>
       <c r="I6" t="n">
-        <v>3.450886972857674e-05</v>
+        <v>0.002169702249624809</v>
       </c>
       <c r="J6" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K6" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L6" t="n">
-        <v>6.439910715805297e-09</v>
+        <v>2.548197402896246e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.533543334478509</v>
+        <v>2.538858761118108</v>
       </c>
       <c r="N6" t="n">
-        <v>9.68185554714727</v>
+        <v>9.701515857169774</v>
       </c>
       <c r="O6" t="n">
-        <v>3.111568020652493</v>
+        <v>3.114725647175008</v>
       </c>
       <c r="P6" t="n">
-        <v>380.3785209592707</v>
+        <v>380.3562271242644</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -21068,28 +21117,28 @@
         <v>0.1858</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01097662503884476</v>
+        <v>-0.01053361576800879</v>
       </c>
       <c r="J7" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K7" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001186825105724987</v>
+        <v>0.001098673656100724</v>
       </c>
       <c r="M7" t="n">
-        <v>1.79696418631849</v>
+        <v>1.794455882329528</v>
       </c>
       <c r="N7" t="n">
-        <v>5.308993184782096</v>
+        <v>5.297759986556594</v>
       </c>
       <c r="O7" t="n">
-        <v>2.30412525370955</v>
+        <v>2.301686335397722</v>
       </c>
       <c r="P7" t="n">
-        <v>380.5096794242859</v>
+        <v>380.5050539062025</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -21150,28 +21199,28 @@
         <v>0.1404</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04263708252381359</v>
+        <v>0.04341446974059594</v>
       </c>
       <c r="J8" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K8" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01984369378486206</v>
+        <v>0.02064463492979829</v>
       </c>
       <c r="M8" t="n">
-        <v>1.754764746636785</v>
+        <v>1.7547664185792</v>
       </c>
       <c r="N8" t="n">
-        <v>4.70137349144275</v>
+        <v>4.695540126167448</v>
       </c>
       <c r="O8" t="n">
-        <v>2.168265087908475</v>
+        <v>2.16691950154302</v>
       </c>
       <c r="P8" t="n">
-        <v>379.5756654533256</v>
+        <v>379.5675486511145</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -21232,28 +21281,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07830717817905693</v>
+        <v>0.07802261417318371</v>
       </c>
       <c r="J9" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K9" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06368157965485188</v>
+        <v>0.0635645163633185</v>
       </c>
       <c r="M9" t="n">
-        <v>1.713188478158662</v>
+        <v>1.710281363601929</v>
       </c>
       <c r="N9" t="n">
-        <v>4.720520201726183</v>
+        <v>4.709638406486648</v>
       </c>
       <c r="O9" t="n">
-        <v>2.17267581606787</v>
+        <v>2.170170133074052</v>
       </c>
       <c r="P9" t="n">
-        <v>377.5943056835042</v>
+        <v>377.5972768537295</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -21314,28 +21363,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.008823624742741001</v>
+        <v>-0.009084625321093873</v>
       </c>
       <c r="J10" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K10" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001290695474235437</v>
+        <v>0.001375299464326796</v>
       </c>
       <c r="M10" t="n">
-        <v>1.450442126123143</v>
+        <v>1.448196246484661</v>
       </c>
       <c r="N10" t="n">
-        <v>3.154179034824712</v>
+        <v>3.147041903168359</v>
       </c>
       <c r="O10" t="n">
-        <v>1.776000854398644</v>
+        <v>1.77399038981849</v>
       </c>
       <c r="P10" t="n">
-        <v>384.9923471847575</v>
+        <v>384.9950723261359</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -21377,7 +21426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K405"/>
+  <dimension ref="A1:K406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44449,6 +44498,63 @@
         </is>
       </c>
     </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>-36.745637534293856,175.16856493573994</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>-36.746331653318904,175.16869891572475</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>-36.747012785665085,175.1689551751114</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>-36.74769056320812,175.16911414051518</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>-36.748316447753766,175.16947390389285</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>-36.748915572891555,175.1698744204935</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>-36.74946859977828,175.17040326605397</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>-36.749991461056766,175.17099175029693</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>-36.75045779958248,175.17167364189197</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0163/nzd0163.xlsx
+++ b/data/nzd0163/nzd0163.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K406"/>
+  <dimension ref="A1:K407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16270,6 +16270,45 @@
         <v>384.25</v>
       </c>
       <c r="K406" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>363.66</v>
+      </c>
+      <c r="C407" t="n">
+        <v>367.62</v>
+      </c>
+      <c r="D407" t="n">
+        <v>374.92</v>
+      </c>
+      <c r="E407" t="n">
+        <v>373.09</v>
+      </c>
+      <c r="F407" t="n">
+        <v>385.05</v>
+      </c>
+      <c r="G407" t="n">
+        <v>380.72</v>
+      </c>
+      <c r="H407" t="n">
+        <v>380.79</v>
+      </c>
+      <c r="I407" t="n">
+        <v>376.42</v>
+      </c>
+      <c r="J407" t="n">
+        <v>383.45</v>
+      </c>
+      <c r="K407" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -16286,7 +16325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B425"/>
+  <dimension ref="A1:B426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20539,6 +20578,16 @@
       </c>
       <c r="B425" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>-0.2</v>
       </c>
     </row>
   </sheetData>
@@ -20707,34 +20756,30 @@
         <v>0.1573</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04408234725907772</v>
+        <v>-0.04308164576445787</v>
       </c>
       <c r="J2" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K2" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008111339468876988</v>
+        <v>0.007787346987637722</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8341706949959</v>
+        <v>2.832357913588493</v>
       </c>
       <c r="N2" t="n">
-        <v>12.5309158607365</v>
+        <v>12.50934687646962</v>
       </c>
       <c r="O2" t="n">
-        <v>3.539903368841655</v>
+        <v>3.536855506869007</v>
       </c>
       <c r="P2" t="n">
-        <v>362.8560423079612</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>362.8455275412568</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (175.1645428183145 -36.74591678298516, 175.17481514398295 -36.745203319993514)</t>
@@ -20789,34 +20834,30 @@
         <v>0.1392</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0531789682045142</v>
+        <v>-0.05324215061356297</v>
       </c>
       <c r="J3" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K3" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02490787807922323</v>
+        <v>0.02510192113246457</v>
       </c>
       <c r="M3" t="n">
-        <v>1.934135717597186</v>
+        <v>1.929694822194581</v>
       </c>
       <c r="N3" t="n">
-        <v>5.838103273297919</v>
+        <v>5.823690186870948</v>
       </c>
       <c r="O3" t="n">
-        <v>2.416216727302813</v>
+        <v>2.413232311003429</v>
       </c>
       <c r="P3" t="n">
-        <v>369.1404108907745</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>369.1410747733554</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (175.1646278384432 -36.74678241643596, 175.17484197375498 -36.745651201228185)</t>
@@ -20871,34 +20912,30 @@
         <v>0.1896</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04199314393522962</v>
+        <v>-0.04332816697589834</v>
       </c>
       <c r="J4" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K4" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02123369778734552</v>
+        <v>0.02261147159836907</v>
       </c>
       <c r="M4" t="n">
-        <v>1.540109968294721</v>
+        <v>1.542245893251458</v>
       </c>
       <c r="N4" t="n">
-        <v>4.268680132187119</v>
+        <v>4.27488160652834</v>
       </c>
       <c r="O4" t="n">
-        <v>2.066078442892989</v>
+        <v>2.067578682064685</v>
       </c>
       <c r="P4" t="n">
-        <v>378.6409178781099</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>378.6549612750756</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (175.16484913664593 -36.74778721263662, 175.1748870206051 -36.74589372341795)</t>
@@ -20953,34 +20990,30 @@
         <v>0.1049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008214857728779508</v>
+        <v>0.00853350896741367</v>
       </c>
       <c r="J5" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K5" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003641291861912199</v>
+        <v>0.000395081997388913</v>
       </c>
       <c r="M5" t="n">
-        <v>2.464285371004699</v>
+        <v>2.459581905779747</v>
       </c>
       <c r="N5" t="n">
-        <v>9.729037762086994</v>
+        <v>9.706026911322462</v>
       </c>
       <c r="O5" t="n">
-        <v>3.119140548626655</v>
+        <v>3.115449712533082</v>
       </c>
       <c r="P5" t="n">
-        <v>372.249954923965</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>372.2466029624621</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (175.16511533793658 -36.748592005854064, 175.17504279455974 -36.74635379416353)</t>
@@ -21035,34 +21068,30 @@
         <v>0.104</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002169702249624809</v>
+        <v>0.004535067573759126</v>
       </c>
       <c r="J6" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K6" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L6" t="n">
-        <v>2.548197402896246e-05</v>
+        <v>0.0001113389692175559</v>
       </c>
       <c r="M6" t="n">
-        <v>2.538858761118108</v>
+        <v>2.545313262350938</v>
       </c>
       <c r="N6" t="n">
-        <v>9.701515857169774</v>
+        <v>9.730093678269656</v>
       </c>
       <c r="O6" t="n">
-        <v>3.114725647175008</v>
+        <v>3.119309807997541</v>
       </c>
       <c r="P6" t="n">
-        <v>380.3562271242644</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>380.3313453333112</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (175.16552709096803 -36.74970277782533, 175.1749746175794 -36.746384007586755)</t>
@@ -21117,34 +21146,30 @@
         <v>0.1858</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01053361576800879</v>
+        <v>-0.01028143791196481</v>
       </c>
       <c r="J7" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K7" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001098673656100724</v>
+        <v>0.001052507369630584</v>
       </c>
       <c r="M7" t="n">
-        <v>1.794455882329528</v>
+        <v>1.791111600210171</v>
       </c>
       <c r="N7" t="n">
-        <v>5.297759986556594</v>
+        <v>5.285307740255459</v>
       </c>
       <c r="O7" t="n">
-        <v>2.301686335397722</v>
+        <v>2.298979717234465</v>
       </c>
       <c r="P7" t="n">
-        <v>380.5050539062025</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>380.5024011926309</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (175.1663587372637 -36.75086185072126, 175.17484940202218 -36.74616108987176)</t>
@@ -21199,34 +21224,30 @@
         <v>0.1404</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04341446974059594</v>
+        <v>0.04345521217820826</v>
       </c>
       <c r="J8" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K8" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02064463492979829</v>
+        <v>0.02079628975978731</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7547664185792</v>
+        <v>1.750667647999799</v>
       </c>
       <c r="N8" t="n">
-        <v>4.695540126167448</v>
+        <v>4.683990324474949</v>
       </c>
       <c r="O8" t="n">
-        <v>2.16691950154302</v>
+        <v>2.164252832844386</v>
       </c>
       <c r="P8" t="n">
-        <v>379.5675486511145</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>379.5671200725752</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (175.16718844204436 -36.75174210551324, 175.17492836692847 -36.746268106654135)</t>
@@ -21281,34 +21302,30 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07802261417318371</v>
+        <v>0.07637591319808951</v>
       </c>
       <c r="J9" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K9" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0635645163633185</v>
+        <v>0.06108347400338165</v>
       </c>
       <c r="M9" t="n">
-        <v>1.710281363601929</v>
+        <v>1.713603386991757</v>
       </c>
       <c r="N9" t="n">
-        <v>4.709638406486648</v>
+        <v>4.723469720796319</v>
       </c>
       <c r="O9" t="n">
-        <v>2.170170133074052</v>
+        <v>2.173354485765338</v>
       </c>
       <c r="P9" t="n">
-        <v>377.5972768537295</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>377.6145988584984</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>LINESTRING (175.1680364596389 -36.75244335853723, 175.17520957634764 -36.746491695389324)</t>
@@ -21363,34 +21380,30 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.009084625321093873</v>
+        <v>-0.009750191461306096</v>
       </c>
       <c r="J10" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K10" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001375299464326796</v>
+        <v>0.001590648044181076</v>
       </c>
       <c r="M10" t="n">
-        <v>1.448196246484661</v>
+        <v>1.447973117041149</v>
       </c>
       <c r="N10" t="n">
-        <v>3.147041903168359</v>
+        <v>3.143445112546876</v>
       </c>
       <c r="O10" t="n">
-        <v>1.77399038981849</v>
+        <v>1.772976342917997</v>
       </c>
       <c r="P10" t="n">
-        <v>384.9950723261359</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>385.0020735607432</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>LINESTRING (175.16871809100408 -36.75297400438908, 175.17579516505327 -36.7469485579063)</t>
@@ -21426,7 +21439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K406"/>
+  <dimension ref="A1:K407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44555,6 +44568,63 @@
         </is>
       </c>
     </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>-36.745635132801226,175.16859951669102</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>-36.74633091630375,175.16870557102956</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>-36.74701634302206,175.1689363157736</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>-36.74768519129675,175.1691379682833</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>-36.74831482560852,175.16947852176227</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>-36.74891751360085,175.1698709150478</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>-36.74947710579906,175.17039123878598</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>-36.7500086662309,175.17097101371138</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>-36.75046303833598,175.17166748870065</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0163/nzd0163.xlsx
+++ b/data/nzd0163/nzd0163.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K407"/>
+  <dimension ref="A1:K409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16311,6 +16311,84 @@
       <c r="K407" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>363.66</v>
+      </c>
+      <c r="C408" t="n">
+        <v>367.23</v>
+      </c>
+      <c r="D408" t="n">
+        <v>376.34</v>
+      </c>
+      <c r="E408" t="n">
+        <v>373.59</v>
+      </c>
+      <c r="F408" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="G408" t="n">
+        <v>381.1</v>
+      </c>
+      <c r="H408" t="n">
+        <v>380.75</v>
+      </c>
+      <c r="I408" t="n">
+        <v>377.54</v>
+      </c>
+      <c r="J408" t="n">
+        <v>383.25</v>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="C409" t="n">
+        <v>367.23</v>
+      </c>
+      <c r="D409" t="n">
+        <v>376.34</v>
+      </c>
+      <c r="E409" t="n">
+        <v>373.59</v>
+      </c>
+      <c r="F409" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="G409" t="n">
+        <v>381.1</v>
+      </c>
+      <c r="H409" t="n">
+        <v>380.75</v>
+      </c>
+      <c r="I409" t="n">
+        <v>377.54</v>
+      </c>
+      <c r="J409" t="n">
+        <v>383.25</v>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16325,7 +16403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B426"/>
+  <dimension ref="A1:B428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20588,6 +20666,26 @@
       </c>
       <c r="B426" t="n">
         <v>-0.2</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>
@@ -20756,28 +20854,28 @@
         <v>0.1573</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04308164576445787</v>
+        <v>-0.04094261735484521</v>
       </c>
       <c r="J2" t="n">
+        <v>408</v>
+      </c>
+      <c r="K2" t="n">
         <v>406</v>
       </c>
-      <c r="K2" t="n">
-        <v>404</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.007787346987637722</v>
+        <v>0.007104633760920853</v>
       </c>
       <c r="M2" t="n">
-        <v>2.832357913588493</v>
+        <v>2.82939578963287</v>
       </c>
       <c r="N2" t="n">
-        <v>12.50934687646962</v>
+        <v>12.46954941129496</v>
       </c>
       <c r="O2" t="n">
-        <v>3.536855506869007</v>
+        <v>3.531224916554447</v>
       </c>
       <c r="P2" t="n">
-        <v>362.8455275412568</v>
+        <v>362.8229769725639</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20834,28 +20932,28 @@
         <v>0.1392</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05324215061356297</v>
+        <v>-0.05375451786565</v>
       </c>
       <c r="J3" t="n">
+        <v>408</v>
+      </c>
+      <c r="K3" t="n">
         <v>406</v>
       </c>
-      <c r="K3" t="n">
-        <v>404</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02510192113246457</v>
+        <v>0.02584919473284031</v>
       </c>
       <c r="M3" t="n">
-        <v>1.929694822194581</v>
+        <v>1.922966325980405</v>
       </c>
       <c r="N3" t="n">
-        <v>5.823690186870948</v>
+        <v>5.796247001875823</v>
       </c>
       <c r="O3" t="n">
-        <v>2.413232311003429</v>
+        <v>2.407539615847644</v>
       </c>
       <c r="P3" t="n">
-        <v>369.1410747733554</v>
+        <v>369.1464757519757</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20912,28 +21010,28 @@
         <v>0.1896</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04332816697589834</v>
+        <v>-0.0445134909410619</v>
       </c>
       <c r="J4" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K4" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02261147159836907</v>
+        <v>0.02406068682679607</v>
       </c>
       <c r="M4" t="n">
-        <v>1.542245893251458</v>
+        <v>1.540025539891404</v>
       </c>
       <c r="N4" t="n">
-        <v>4.27488160652834</v>
+        <v>4.260549551839911</v>
       </c>
       <c r="O4" t="n">
-        <v>2.067578682064685</v>
+        <v>2.064109869130011</v>
       </c>
       <c r="P4" t="n">
-        <v>378.6549612750756</v>
+        <v>378.6674698211838</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20990,28 +21088,28 @@
         <v>0.1049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00853350896741367</v>
+        <v>0.009665083749993872</v>
       </c>
       <c r="J5" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K5" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000395081997388913</v>
+        <v>0.0005121269104265691</v>
       </c>
       <c r="M5" t="n">
-        <v>2.459581905779747</v>
+        <v>2.452317465250355</v>
       </c>
       <c r="N5" t="n">
-        <v>9.706026911322462</v>
+        <v>9.664484500414007</v>
       </c>
       <c r="O5" t="n">
-        <v>3.115449712533082</v>
+        <v>3.108775402053678</v>
       </c>
       <c r="P5" t="n">
-        <v>372.2466029624621</v>
+        <v>372.2346616075407</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21068,28 +21166,28 @@
         <v>0.104</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004535067573759126</v>
+        <v>0.008631098997563367</v>
       </c>
       <c r="J6" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K6" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001113389692175559</v>
+        <v>0.0004043971447715844</v>
       </c>
       <c r="M6" t="n">
-        <v>2.545313262350938</v>
+        <v>2.554820892625411</v>
       </c>
       <c r="N6" t="n">
-        <v>9.730093678269656</v>
+        <v>9.761486788563198</v>
       </c>
       <c r="O6" t="n">
-        <v>3.119309807997541</v>
+        <v>3.12433781601209</v>
       </c>
       <c r="P6" t="n">
-        <v>380.3313453333112</v>
+        <v>380.28812045752</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21146,28 +21244,28 @@
         <v>0.1858</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01028143791196481</v>
+        <v>-0.009398956513976328</v>
       </c>
       <c r="J7" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K7" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001052507369630584</v>
+        <v>0.0008889991589681179</v>
       </c>
       <c r="M7" t="n">
-        <v>1.791111600210171</v>
+        <v>1.786047639123095</v>
       </c>
       <c r="N7" t="n">
-        <v>5.285307740255459</v>
+        <v>5.263070527594894</v>
       </c>
       <c r="O7" t="n">
-        <v>2.298979717234465</v>
+        <v>2.29413829739946</v>
       </c>
       <c r="P7" t="n">
-        <v>380.5024011926309</v>
+        <v>380.4930884781581</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21224,28 +21322,28 @@
         <v>0.1404</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04345521217820826</v>
+        <v>0.04349602557049009</v>
       </c>
       <c r="J8" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K8" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02079628975978731</v>
+        <v>0.02106388274134652</v>
       </c>
       <c r="M8" t="n">
-        <v>1.750667647999799</v>
+        <v>1.742307445461759</v>
       </c>
       <c r="N8" t="n">
-        <v>4.683990324474949</v>
+        <v>4.661037451596635</v>
       </c>
       <c r="O8" t="n">
-        <v>2.164252832844386</v>
+        <v>2.158943596205476</v>
       </c>
       <c r="P8" t="n">
-        <v>379.5671200725752</v>
+        <v>379.5666893952618</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21302,28 +21400,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07637591319808951</v>
+        <v>0.07426153874043911</v>
       </c>
       <c r="J9" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K9" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06108347400338165</v>
+        <v>0.05830879443603731</v>
       </c>
       <c r="M9" t="n">
-        <v>1.713603386991757</v>
+        <v>1.714783596335929</v>
       </c>
       <c r="N9" t="n">
-        <v>4.723469720796319</v>
+        <v>4.7213898110117</v>
       </c>
       <c r="O9" t="n">
-        <v>2.173354485765338</v>
+        <v>2.172875930883238</v>
       </c>
       <c r="P9" t="n">
-        <v>377.6145988584984</v>
+        <v>377.6369116095015</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21380,28 +21478,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.009750191461306096</v>
+        <v>-0.01126072950052879</v>
       </c>
       <c r="J10" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K10" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001590648044181076</v>
+        <v>0.002137021609613488</v>
       </c>
       <c r="M10" t="n">
-        <v>1.447973117041149</v>
+        <v>1.44837524691806</v>
       </c>
       <c r="N10" t="n">
-        <v>3.143445112546876</v>
+        <v>3.138792219214651</v>
       </c>
       <c r="O10" t="n">
-        <v>1.772976342917997</v>
+        <v>1.771663686825084</v>
       </c>
       <c r="P10" t="n">
-        <v>385.0020735607432</v>
+        <v>385.0180140642121</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21439,7 +21537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K407"/>
+  <dimension ref="A1:K409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44625,6 +44723,120 @@
         </is>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>-36.745635132801226,175.16859951669102</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>-36.74633139536363,175.16870124508145</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>-36.747013423110765,175.16895179569264</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>-36.74768397593155,175.16914335918057</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>-36.748316808230456,175.1694728776996</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>-36.748915572891555,175.1698744204935</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>-36.749477343729694,175.17039090235886</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>-36.750001421947445,175.17097974490645</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>-36.75046434802432,175.1716659504027</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>-36.745634877157876,175.16860319788887</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>-36.74633139536363,175.16870124508145</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>-36.747013423110765,175.16895179569264</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>-36.74768397593155,175.16914335918057</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>-36.748316808230456,175.1694728776996</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>-36.748915572891555,175.1698744204935</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>-36.749477343729694,175.17039090235886</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>-36.750001421947445,175.17097974490645</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>-36.75046434802432,175.1716659504027</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0163/nzd0163.xlsx
+++ b/data/nzd0163/nzd0163.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K409"/>
+  <dimension ref="A1:K410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16389,6 +16389,45 @@
       <c r="K409" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>365.73</v>
+      </c>
+      <c r="C410" t="n">
+        <v>367.52</v>
+      </c>
+      <c r="D410" t="n">
+        <v>376.88</v>
+      </c>
+      <c r="E410" t="n">
+        <v>373.28</v>
+      </c>
+      <c r="F410" t="n">
+        <v>383.79</v>
+      </c>
+      <c r="G410" t="n">
+        <v>381.31</v>
+      </c>
+      <c r="H410" t="n">
+        <v>379.3</v>
+      </c>
+      <c r="I410" t="n">
+        <v>376.86</v>
+      </c>
+      <c r="J410" t="n">
+        <v>383.05</v>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16403,7 +16442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B428"/>
+  <dimension ref="A1:B429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20686,6 +20725,16 @@
       </c>
       <c r="B428" t="n">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>-0.68</v>
       </c>
     </row>
   </sheetData>
@@ -20854,28 +20903,28 @@
         <v>0.1573</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04094261735484521</v>
+        <v>-0.03893184086278443</v>
       </c>
       <c r="J2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K2" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007104633760920853</v>
+        <v>0.006443869619796483</v>
       </c>
       <c r="M2" t="n">
-        <v>2.82939578963287</v>
+        <v>2.832703345694465</v>
       </c>
       <c r="N2" t="n">
-        <v>12.46954941129496</v>
+        <v>12.47770794099068</v>
       </c>
       <c r="O2" t="n">
-        <v>3.531224916554447</v>
+        <v>3.532379925912652</v>
       </c>
       <c r="P2" t="n">
-        <v>362.8229769725639</v>
+        <v>362.8017319618023</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20932,28 +20981,28 @@
         <v>0.1392</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05375451786565</v>
+        <v>-0.05386123489977112</v>
       </c>
       <c r="J3" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K3" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02584919473284031</v>
+        <v>0.02608941007213761</v>
       </c>
       <c r="M3" t="n">
-        <v>1.922966325980405</v>
+        <v>1.918815779658821</v>
       </c>
       <c r="N3" t="n">
-        <v>5.796247001875823</v>
+        <v>5.782114885953359</v>
       </c>
       <c r="O3" t="n">
-        <v>2.407539615847644</v>
+        <v>2.404602854101558</v>
       </c>
       <c r="P3" t="n">
-        <v>369.1464757519757</v>
+        <v>369.1476032788527</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21010,28 +21059,28 @@
         <v>0.1896</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0445134909410619</v>
+        <v>-0.04482443268891909</v>
       </c>
       <c r="J4" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K4" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02406068682679607</v>
+        <v>0.02451722151296187</v>
       </c>
       <c r="M4" t="n">
-        <v>1.540025539891404</v>
+        <v>1.537697722778773</v>
       </c>
       <c r="N4" t="n">
-        <v>4.260549551839911</v>
+        <v>4.2510548114424</v>
       </c>
       <c r="O4" t="n">
-        <v>2.064109869130011</v>
+        <v>2.061808626289647</v>
       </c>
       <c r="P4" t="n">
-        <v>378.6674698211838</v>
+        <v>378.6707586530841</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21088,28 +21137,28 @@
         <v>0.1049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009665083749993872</v>
+        <v>0.0100623135901819</v>
       </c>
       <c r="J5" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K5" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005121269104265691</v>
+        <v>0.0005580699796915445</v>
       </c>
       <c r="M5" t="n">
-        <v>2.452317465250355</v>
+        <v>2.448003251857484</v>
       </c>
       <c r="N5" t="n">
-        <v>9.664484500414007</v>
+        <v>9.64236008695169</v>
       </c>
       <c r="O5" t="n">
-        <v>3.108775402053678</v>
+        <v>3.105214982404872</v>
       </c>
       <c r="P5" t="n">
-        <v>372.2346616075407</v>
+        <v>372.230460106201</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21166,28 +21215,28 @@
         <v>0.104</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008631098997563367</v>
+        <v>0.01028006760792896</v>
       </c>
       <c r="J6" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K6" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004043971447715844</v>
+        <v>0.000575244838490363</v>
       </c>
       <c r="M6" t="n">
-        <v>2.554820892625411</v>
+        <v>2.557366919058124</v>
       </c>
       <c r="N6" t="n">
-        <v>9.761486788563198</v>
+        <v>9.763556844547228</v>
       </c>
       <c r="O6" t="n">
-        <v>3.12433781601209</v>
+        <v>3.124669077606016</v>
       </c>
       <c r="P6" t="n">
-        <v>380.28812045752</v>
+        <v>380.2706793110486</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21244,28 +21293,28 @@
         <v>0.1858</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.009398956513976328</v>
+        <v>-0.008861931801127468</v>
       </c>
       <c r="J7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008889991589681179</v>
+        <v>0.0007943774010554794</v>
       </c>
       <c r="M7" t="n">
-        <v>1.786047639123095</v>
+        <v>1.783923776690115</v>
       </c>
       <c r="N7" t="n">
-        <v>5.263070527594894</v>
+        <v>5.252953315435423</v>
       </c>
       <c r="O7" t="n">
-        <v>2.29413829739946</v>
+        <v>2.29193222313301</v>
       </c>
       <c r="P7" t="n">
-        <v>380.4930884781581</v>
+        <v>380.4874083659858</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21322,28 +21371,28 @@
         <v>0.1404</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04349602557049009</v>
+        <v>0.04278266246008618</v>
       </c>
       <c r="J8" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K8" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02106388274134652</v>
+        <v>0.02048300776022172</v>
       </c>
       <c r="M8" t="n">
-        <v>1.742307445461759</v>
+        <v>1.741070775312253</v>
       </c>
       <c r="N8" t="n">
-        <v>4.661037451596635</v>
+        <v>4.654495413589032</v>
       </c>
       <c r="O8" t="n">
-        <v>2.158943596205476</v>
+        <v>2.157427962549163</v>
       </c>
       <c r="P8" t="n">
-        <v>379.5666893952618</v>
+        <v>379.574234639251</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21400,28 +21449,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07426153874043911</v>
+        <v>0.07288042887883971</v>
       </c>
       <c r="J9" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K9" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05830879443603731</v>
+        <v>0.05637160038648048</v>
       </c>
       <c r="M9" t="n">
-        <v>1.714783596335929</v>
+        <v>1.716801062983493</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7213898110117</v>
+        <v>4.72804088368046</v>
       </c>
       <c r="O9" t="n">
-        <v>2.172875930883238</v>
+        <v>2.174405869123899</v>
       </c>
       <c r="P9" t="n">
-        <v>377.6369116095015</v>
+        <v>377.6515196130971</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21478,28 +21527,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01126072950052879</v>
+        <v>-0.01210224314010113</v>
       </c>
       <c r="J10" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K10" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002137021609613488</v>
+        <v>0.00247593108499522</v>
       </c>
       <c r="M10" t="n">
-        <v>1.44837524691806</v>
+        <v>1.4489881096984</v>
       </c>
       <c r="N10" t="n">
-        <v>3.138792219214651</v>
+        <v>3.137872725684585</v>
       </c>
       <c r="O10" t="n">
-        <v>1.771663686825084</v>
+        <v>1.771404167795872</v>
       </c>
       <c r="P10" t="n">
-        <v>385.0180140642121</v>
+        <v>385.0269147567743</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21537,7 +21586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K409"/>
+  <dimension ref="A1:K410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44837,6 +44886,63 @@
         </is>
       </c>
     </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>-36.745633529218324,175.16862260784075</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>-36.746331039139626,175.1687044618121</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>-36.747012312721445,175.16895768242208</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>-36.74768472945801,175.1691400168243</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>-36.74831936761478,175.16946559172732</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>-36.748914500394264,175.1698763577134</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>-36.7494859687146,175.17037870687452</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>-36.75000582026246,175.17097444382392</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>-36.750465657712624,175.1716644121047</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0163/nzd0163.xlsx
+++ b/data/nzd0163/nzd0163.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K410"/>
+  <dimension ref="A1:K414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16428,6 +16428,162 @@
       <c r="K410" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>364.31</v>
+      </c>
+      <c r="C411" t="n">
+        <v>366.38</v>
+      </c>
+      <c r="D411" t="n">
+        <v>377.75</v>
+      </c>
+      <c r="E411" t="n">
+        <v>373.12</v>
+      </c>
+      <c r="F411" t="n">
+        <v>384.01</v>
+      </c>
+      <c r="G411" t="n">
+        <v>380.72</v>
+      </c>
+      <c r="H411" t="n">
+        <v>379.29</v>
+      </c>
+      <c r="I411" t="n">
+        <v>377.41</v>
+      </c>
+      <c r="J411" t="n">
+        <v>382.83</v>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>363.32</v>
+      </c>
+      <c r="C412" t="n">
+        <v>366</v>
+      </c>
+      <c r="D412" t="n">
+        <v>377.42</v>
+      </c>
+      <c r="E412" t="n">
+        <v>373.81</v>
+      </c>
+      <c r="F412" t="n">
+        <v>384.31</v>
+      </c>
+      <c r="G412" t="n">
+        <v>381.18</v>
+      </c>
+      <c r="H412" t="n">
+        <v>379.13</v>
+      </c>
+      <c r="I412" t="n">
+        <v>378.44</v>
+      </c>
+      <c r="J412" t="n">
+        <v>382.59</v>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>362.48</v>
+      </c>
+      <c r="C413" t="n">
+        <v>367.69</v>
+      </c>
+      <c r="D413" t="n">
+        <v>377.38</v>
+      </c>
+      <c r="E413" t="n">
+        <v>373.57</v>
+      </c>
+      <c r="F413" t="n">
+        <v>384.68</v>
+      </c>
+      <c r="G413" t="n">
+        <v>381.26</v>
+      </c>
+      <c r="H413" t="n">
+        <v>379.89</v>
+      </c>
+      <c r="I413" t="n">
+        <v>378.89</v>
+      </c>
+      <c r="J413" t="n">
+        <v>383.01</v>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>362.9</v>
+      </c>
+      <c r="C414" t="n">
+        <v>367.61</v>
+      </c>
+      <c r="D414" t="n">
+        <v>377.45</v>
+      </c>
+      <c r="E414" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="F414" t="n">
+        <v>384.58</v>
+      </c>
+      <c r="G414" t="n">
+        <v>381.56</v>
+      </c>
+      <c r="H414" t="n">
+        <v>379.79</v>
+      </c>
+      <c r="I414" t="n">
+        <v>378.81</v>
+      </c>
+      <c r="J414" t="n">
+        <v>383.45</v>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16442,7 +16598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B429"/>
+  <dimension ref="A1:B433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20735,6 +20891,46 @@
       </c>
       <c r="B429" t="n">
         <v>-0.68</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>-0.85</v>
       </c>
     </row>
   </sheetData>
@@ -20903,28 +21099,28 @@
         <v>0.1573</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03893184086278443</v>
+        <v>-0.03600239138614926</v>
       </c>
       <c r="J2" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K2" t="n">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006443869619796483</v>
+        <v>0.00562689122629334</v>
       </c>
       <c r="M2" t="n">
-        <v>2.832703345694465</v>
+        <v>2.819827133352015</v>
       </c>
       <c r="N2" t="n">
-        <v>12.47770794099068</v>
+        <v>12.38153596290876</v>
       </c>
       <c r="O2" t="n">
-        <v>3.532379925912652</v>
+        <v>3.518740678553729</v>
       </c>
       <c r="P2" t="n">
-        <v>362.8017319618023</v>
+        <v>362.7706375599723</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20981,28 +21177,28 @@
         <v>0.1392</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05386123489977112</v>
+        <v>-0.05543791584255062</v>
       </c>
       <c r="J3" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K3" t="n">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02608941007213761</v>
+        <v>0.02814119977356422</v>
       </c>
       <c r="M3" t="n">
-        <v>1.918815779658821</v>
+        <v>1.908464664000844</v>
       </c>
       <c r="N3" t="n">
-        <v>5.782114885953359</v>
+        <v>5.737270502815298</v>
       </c>
       <c r="O3" t="n">
-        <v>2.404602854101558</v>
+        <v>2.395260007351039</v>
       </c>
       <c r="P3" t="n">
-        <v>369.1476032788527</v>
+        <v>369.1643323434231</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21059,28 +21255,28 @@
         <v>0.1896</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04482443268891909</v>
+        <v>-0.04479181230038481</v>
       </c>
       <c r="J4" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K4" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02451722151296187</v>
+        <v>0.02501568529367815</v>
       </c>
       <c r="M4" t="n">
-        <v>1.537697722778773</v>
+        <v>1.523941561581445</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2510548114424</v>
+        <v>4.210091433394199</v>
       </c>
       <c r="O4" t="n">
-        <v>2.061808626289647</v>
+        <v>2.051850733702186</v>
       </c>
       <c r="P4" t="n">
-        <v>378.6707586530841</v>
+        <v>378.6704141822063</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21137,28 +21333,28 @@
         <v>0.1049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0100623135901819</v>
+        <v>0.01194214986688092</v>
       </c>
       <c r="J5" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K5" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005580699796915445</v>
+        <v>0.0008026989540603768</v>
       </c>
       <c r="M5" t="n">
-        <v>2.448003251857484</v>
+        <v>2.432331592772844</v>
       </c>
       <c r="N5" t="n">
-        <v>9.64236008695169</v>
+        <v>9.558123189906819</v>
       </c>
       <c r="O5" t="n">
-        <v>3.105214982404872</v>
+        <v>3.091621449968741</v>
       </c>
       <c r="P5" t="n">
-        <v>372.230460106201</v>
+        <v>372.2104773016463</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21215,28 +21411,28 @@
         <v>0.104</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01028006760792896</v>
+        <v>0.017887657516456</v>
       </c>
       <c r="J6" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K6" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000575244838490363</v>
+        <v>0.001753230204768697</v>
       </c>
       <c r="M6" t="n">
-        <v>2.557366919058124</v>
+        <v>2.573004166155714</v>
       </c>
       <c r="N6" t="n">
-        <v>9.763556844547228</v>
+        <v>9.8087789199919</v>
       </c>
       <c r="O6" t="n">
-        <v>3.124669077606016</v>
+        <v>3.131897016185542</v>
       </c>
       <c r="P6" t="n">
-        <v>380.2706793110486</v>
+        <v>380.189808003975</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21293,28 +21489,28 @@
         <v>0.1858</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.008861931801127468</v>
+        <v>-0.00702744183667179</v>
       </c>
       <c r="J7" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K7" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007943774010554794</v>
+        <v>0.0005099848195114776</v>
       </c>
       <c r="M7" t="n">
-        <v>1.783923776690115</v>
+        <v>1.774133291881291</v>
       </c>
       <c r="N7" t="n">
-        <v>5.252953315435423</v>
+        <v>5.211044298617288</v>
       </c>
       <c r="O7" t="n">
-        <v>2.29193222313301</v>
+        <v>2.282771188406163</v>
       </c>
       <c r="P7" t="n">
-        <v>380.4874083659858</v>
+        <v>380.4679020007765</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21371,28 +21567,28 @@
         <v>0.1404</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04278266246008618</v>
+        <v>0.04044007564460755</v>
       </c>
       <c r="J8" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K8" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02048300776022172</v>
+        <v>0.01868777410055156</v>
       </c>
       <c r="M8" t="n">
-        <v>1.741070775312253</v>
+        <v>1.733927713949027</v>
       </c>
       <c r="N8" t="n">
-        <v>4.654495413589032</v>
+        <v>4.623624825493478</v>
       </c>
       <c r="O8" t="n">
-        <v>2.157427962549163</v>
+        <v>2.150261571412529</v>
       </c>
       <c r="P8" t="n">
-        <v>379.574234639251</v>
+        <v>379.5991301513996</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21449,28 +21645,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07288042887883971</v>
+        <v>0.07052001185079189</v>
       </c>
       <c r="J9" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K9" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05637160038648048</v>
+        <v>0.05390880322109259</v>
       </c>
       <c r="M9" t="n">
-        <v>1.716801062983493</v>
+        <v>1.710587103814805</v>
       </c>
       <c r="N9" t="n">
-        <v>4.72804088368046</v>
+        <v>4.69901789039675</v>
       </c>
       <c r="O9" t="n">
-        <v>2.174405869123899</v>
+        <v>2.167721820344287</v>
       </c>
       <c r="P9" t="n">
-        <v>377.6515196130971</v>
+        <v>377.6765988845897</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21527,28 +21723,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01210224314010113</v>
+        <v>-0.01552663202836575</v>
       </c>
       <c r="J10" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K10" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00247593108499522</v>
+        <v>0.004121027214456952</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4489881096984</v>
+        <v>1.45207698265553</v>
       </c>
       <c r="N10" t="n">
-        <v>3.137872725684585</v>
+        <v>3.136639705785656</v>
       </c>
       <c r="O10" t="n">
-        <v>1.771404167795872</v>
+        <v>1.771056098994511</v>
       </c>
       <c r="P10" t="n">
-        <v>385.0269147567743</v>
+        <v>385.0633094524898</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21586,7 +21782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K410"/>
+  <dimension ref="A1:K414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44943,6 +45139,234 @@
         </is>
       </c>
     </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>-36.74563462926118,175.16860676753524</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>-36.74633243946799,175.16869181673283</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>-36.747010523760274,175.1689671665969</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-36.747685118374854,175.16913829173714</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>-36.74831857456616,175.1694678493526</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>-36.74891751360085,175.1698709150478</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>-36.749486028197246,175.17037862276774</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>-36.75000226280181,175.17097873146423</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>-36.75046709836976,175.1716627199768</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>-36.745635396191226,175.16859572394165</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>-36.746332906243794,175.1686876017063</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>-36.74701120233183,175.16896356915132</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-36.747683441170786,175.1691457311753</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>-36.74831749313617,175.16947092793242</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>-36.748915164321154,175.16987515848203</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>-36.74948697991965,175.17037727705895</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-36.74999560064785,175.1709867610441</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>-36.750468669995676,175.17166087401904</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>-36.74563604691895,175.16858635361962</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>-36.74633083031862,175.1687063474818</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>-36.747011284582925,175.16896313309732</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-36.74768402454616,175.1691431435447</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>-36.7483161593724,175.16947472484742</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>-36.74891475575077,175.1698758964706</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>-36.74948245923812,175.17038366917538</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>-36.74999268999789,175.17099026911256</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>-36.75046591965029,175.17166410444509</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>-36.74563572155519,175.16859103878068</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>-36.74633092858734,175.16870546010782</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>-36.74701114064352,175.16896389619183</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-36.747684680843406,175.1691402324602</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>-36.74831651984911,175.1694736986542</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>-36.748913223611744,175.16987866392756</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>-36.74948305406466,175.17038282810748</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>-36.74999320744677,175.170989645456</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>-36.75046303833598,175.17166748870065</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0163/nzd0163.xlsx
+++ b/data/nzd0163/nzd0163.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K414"/>
+  <dimension ref="A1:K416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16582,6 +16582,84 @@
         <v>383.45</v>
       </c>
       <c r="K414" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>362.31</v>
+      </c>
+      <c r="C415" t="n">
+        <v>368.08</v>
+      </c>
+      <c r="D415" t="n">
+        <v>378.35</v>
+      </c>
+      <c r="E415" t="n">
+        <v>373.14</v>
+      </c>
+      <c r="F415" t="n">
+        <v>384.08</v>
+      </c>
+      <c r="G415" t="n">
+        <v>382.23</v>
+      </c>
+      <c r="H415" t="n">
+        <v>380.16</v>
+      </c>
+      <c r="I415" t="n">
+        <v>379.08</v>
+      </c>
+      <c r="J415" t="n">
+        <v>383.84</v>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="C416" t="n">
+        <v>367.65</v>
+      </c>
+      <c r="D416" t="n">
+        <v>378.12</v>
+      </c>
+      <c r="E416" t="n">
+        <v>372.48</v>
+      </c>
+      <c r="F416" t="n">
+        <v>383.58</v>
+      </c>
+      <c r="G416" t="n">
+        <v>382.34</v>
+      </c>
+      <c r="H416" t="n">
+        <v>380.12</v>
+      </c>
+      <c r="I416" t="n">
+        <v>378.62</v>
+      </c>
+      <c r="J416" t="n">
+        <v>383.89</v>
+      </c>
+      <c r="K416" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16598,7 +16676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B433"/>
+  <dimension ref="A1:B436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20931,6 +21009,36 @@
       </c>
       <c r="B433" t="n">
         <v>-0.85</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>-0.91</v>
       </c>
     </row>
   </sheetData>
@@ -21099,28 +21207,28 @@
         <v>0.1573</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03600239138614926</v>
+        <v>-0.03605744412056544</v>
       </c>
       <c r="J2" t="n">
+        <v>415</v>
+      </c>
+      <c r="K2" t="n">
         <v>413</v>
       </c>
-      <c r="K2" t="n">
-        <v>411</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.00562689122629334</v>
+        <v>0.005704856591120522</v>
       </c>
       <c r="M2" t="n">
-        <v>2.819827133352015</v>
+        <v>2.808862077439022</v>
       </c>
       <c r="N2" t="n">
-        <v>12.38153596290876</v>
+        <v>12.32309224830383</v>
       </c>
       <c r="O2" t="n">
-        <v>3.518740678553729</v>
+        <v>3.510426220319098</v>
       </c>
       <c r="P2" t="n">
-        <v>362.7706375599723</v>
+        <v>362.7712299245337</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21177,28 +21285,28 @@
         <v>0.1392</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05543791584255062</v>
+        <v>-0.05526866376755608</v>
       </c>
       <c r="J3" t="n">
+        <v>415</v>
+      </c>
+      <c r="K3" t="n">
         <v>413</v>
       </c>
-      <c r="K3" t="n">
-        <v>411</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02814119977356422</v>
+        <v>0.02827076596539035</v>
       </c>
       <c r="M3" t="n">
-        <v>1.908464664000844</v>
+        <v>1.900203208907842</v>
       </c>
       <c r="N3" t="n">
-        <v>5.737270502815298</v>
+        <v>5.709852077322385</v>
       </c>
       <c r="O3" t="n">
-        <v>2.395260007351039</v>
+        <v>2.389529677012274</v>
       </c>
       <c r="P3" t="n">
-        <v>369.1643323434231</v>
+        <v>369.1625297517975</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21255,28 +21363,28 @@
         <v>0.1896</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04479181230038481</v>
+        <v>-0.04404942798948221</v>
       </c>
       <c r="J4" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K4" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02501568529367815</v>
+        <v>0.02445692584042813</v>
       </c>
       <c r="M4" t="n">
-        <v>1.523941561581445</v>
+        <v>1.520433560310403</v>
       </c>
       <c r="N4" t="n">
-        <v>4.210091433394199</v>
+        <v>4.19258160348018</v>
       </c>
       <c r="O4" t="n">
-        <v>2.051850733702186</v>
+        <v>2.047579449857851</v>
       </c>
       <c r="P4" t="n">
-        <v>378.6704141822063</v>
+        <v>378.662491562854</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21333,28 +21441,28 @@
         <v>0.1049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01194214986688092</v>
+        <v>0.01221749451788941</v>
       </c>
       <c r="J5" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K5" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0008026989540603768</v>
+        <v>0.0008492496857798182</v>
       </c>
       <c r="M5" t="n">
-        <v>2.432331592772844</v>
+        <v>2.42205316155985</v>
       </c>
       <c r="N5" t="n">
-        <v>9.558123189906819</v>
+        <v>9.512974318249741</v>
       </c>
       <c r="O5" t="n">
-        <v>3.091621449968741</v>
+        <v>3.084310995708724</v>
       </c>
       <c r="P5" t="n">
-        <v>372.2104773016463</v>
+        <v>372.2075416652398</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21411,28 +21519,28 @@
         <v>0.104</v>
       </c>
       <c r="I6" t="n">
-        <v>0.017887657516456</v>
+        <v>0.02099020483708512</v>
       </c>
       <c r="J6" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K6" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001753230204768697</v>
+        <v>0.002427153249618397</v>
       </c>
       <c r="M6" t="n">
-        <v>2.573004166155714</v>
+        <v>2.577308600647554</v>
       </c>
       <c r="N6" t="n">
-        <v>9.8087789199919</v>
+        <v>9.80928085387178</v>
       </c>
       <c r="O6" t="n">
-        <v>3.131897016185542</v>
+        <v>3.131977147725025</v>
       </c>
       <c r="P6" t="n">
-        <v>380.189808003975</v>
+        <v>380.1566959494376</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21489,28 +21597,28 @@
         <v>0.1858</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.00702744183667179</v>
+        <v>-0.005062605191594101</v>
       </c>
       <c r="J7" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K7" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0005099848195114776</v>
+        <v>0.0002666673364406513</v>
       </c>
       <c r="M7" t="n">
-        <v>1.774133291881291</v>
+        <v>1.773488177022763</v>
       </c>
       <c r="N7" t="n">
-        <v>5.211044298617288</v>
+        <v>5.204977593588985</v>
       </c>
       <c r="O7" t="n">
-        <v>2.282771188406163</v>
+        <v>2.28144199873435</v>
       </c>
       <c r="P7" t="n">
-        <v>380.4679020007765</v>
+        <v>380.446930182196</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21567,28 +21675,28 @@
         <v>0.1404</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04044007564460755</v>
+        <v>0.03991590531577632</v>
       </c>
       <c r="J8" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K8" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01868777410055156</v>
+        <v>0.01840634671560804</v>
       </c>
       <c r="M8" t="n">
-        <v>1.733927713949027</v>
+        <v>1.727712646055583</v>
       </c>
       <c r="N8" t="n">
-        <v>4.623624825493478</v>
+        <v>4.602698267748548</v>
       </c>
       <c r="O8" t="n">
-        <v>2.150261571412529</v>
+        <v>2.145390003647017</v>
       </c>
       <c r="P8" t="n">
-        <v>379.5991301513996</v>
+        <v>379.6047249480109</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21645,28 +21753,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07052001185079189</v>
+        <v>0.06982959460896025</v>
       </c>
       <c r="J9" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K9" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05390880322109259</v>
+        <v>0.05343611641122559</v>
       </c>
       <c r="M9" t="n">
-        <v>1.710587103814805</v>
+        <v>1.705344293310792</v>
       </c>
       <c r="N9" t="n">
-        <v>4.69901789039675</v>
+        <v>4.678972349651899</v>
       </c>
       <c r="O9" t="n">
-        <v>2.167721820344287</v>
+        <v>2.163093236467605</v>
       </c>
       <c r="P9" t="n">
-        <v>377.6765988845897</v>
+        <v>377.6839701126888</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21723,28 +21831,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01552663202836575</v>
+        <v>-0.01629894830830918</v>
       </c>
       <c r="J10" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K10" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004121027214456952</v>
+        <v>0.004584625764576633</v>
       </c>
       <c r="M10" t="n">
-        <v>1.45207698265553</v>
+        <v>1.448947883598594</v>
       </c>
       <c r="N10" t="n">
-        <v>3.136639705785656</v>
+        <v>3.124467509418903</v>
       </c>
       <c r="O10" t="n">
-        <v>1.771056098994511</v>
+        <v>1.767616335469579</v>
       </c>
       <c r="P10" t="n">
-        <v>385.0633094524898</v>
+        <v>385.0715523872294</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21782,7 +21890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K414"/>
+  <dimension ref="A1:K416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45367,6 +45475,120 @@
         </is>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>-36.74563617861377,175.16858445724492</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>-36.74633035125855,175.16871067342979</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>-36.747009289993514,175.16897370740685</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-36.747685069760244,175.16913850737302</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>-36.7483183222325,175.1694685676879</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>-36.74890980183437,175.16988484458102</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-36.749480853206464,175.17038594005868</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>-36.749991461056766,175.17099175029693</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>-36.750460484443686,175.17167048838152</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>-36.74563703850266,175.16857207503327</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>-36.74633087945298,175.1687059037948</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>-36.74700976293747,175.16897120009637</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-36.74768667404199,175.16913139138836</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>-36.7483201246157,175.16946343672137</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>-36.748909240050004,175.16988585931512</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>-36.74948109113708,175.1703856036315</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>-36.74999443638787,175.17098816427153</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>-36.75046015702158,175.17167087295599</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
